--- a/events/Prague_2025_WC/Prague_2025_WC_start.xlsx
+++ b/events/Prague_2025_WC/Prague_2025_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W769"/>
+  <dimension ref="A1:AC769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1428,7 @@
           <t>WOOD Emmi</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>154168</t>
         </is>
@@ -1461,7 +1491,7 @@
           <t>MILLS Waris</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>154167</t>
         </is>
@@ -1524,7 +1554,7 @@
           <t>CHEN Lin</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>87704</t>
         </is>
@@ -1587,7 +1617,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -1650,7 +1680,7 @@
           <t>XIE Xueting</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>130285</t>
         </is>
@@ -1713,7 +1743,7 @@
           <t>WAN Shunfang</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>118852</t>
         </is>
@@ -1776,7 +1806,7 @@
           <t>ALTMAN Marcella</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>97011</t>
         </is>
@@ -1839,7 +1869,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -1902,7 +1932,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -1965,7 +1995,7 @@
           <t>CHANG Chu-Han</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>51896</t>
         </is>
@@ -2028,7 +2058,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -2091,7 +2121,7 @@
           <t>SETCHELL Nikita</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>86250</t>
         </is>
@@ -2154,7 +2184,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>118428</t>
         </is>
@@ -2217,7 +2247,7 @@
           <t>GONI Leire</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>93966</t>
         </is>
@@ -2280,7 +2310,7 @@
           <t>APEL Emily</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>83788</t>
         </is>
@@ -2343,7 +2373,7 @@
           <t>PIETRACHA Eva</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>84043</t>
         </is>
@@ -2406,7 +2436,7 @@
           <t>NESNIDALOVA Lucie</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>75449</t>
         </is>
@@ -2469,7 +2499,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -2532,7 +2562,7 @@
           <t>SRIBAR Ria</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>75645</t>
         </is>
@@ -2595,7 +2625,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -2658,7 +2688,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -2721,7 +2751,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -2784,7 +2814,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -2847,7 +2877,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -2910,7 +2940,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -2973,7 +3003,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -3036,7 +3066,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -3099,7 +3129,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -3162,7 +3192,7 @@
           <t>GALUSKOVA Antonie</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>68754</t>
         </is>
@@ -3225,7 +3255,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -3288,7 +3318,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -3351,7 +3381,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -3414,7 +3444,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -3477,7 +3507,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -3540,7 +3570,7 @@
           <t>SATKOVA Gabriela</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>68786</t>
         </is>
@@ -3603,7 +3633,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -3666,7 +3696,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -3729,7 +3759,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -3792,7 +3822,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -3855,7 +3885,7 @@
           <t>RAW Brayden</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>154169</t>
         </is>
@@ -3918,7 +3948,7 @@
           <t>VAN HEERDEN Matthew</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>143591</t>
         </is>
@@ -3981,7 +4011,7 @@
           <t>ZHANG Hejie</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>130284</t>
         </is>
@@ -4044,7 +4074,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>153722</t>
         </is>
@@ -4107,7 +4137,7 @@
           <t>PARK Moorim</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>100009</t>
         </is>
@@ -4170,7 +4200,7 @@
           <t>MAGAN Raage</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>141057</t>
         </is>
@@ -4233,7 +4263,7 @@
           <t>MAGAN Aar</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>141058</t>
         </is>
@@ -4296,7 +4326,7 @@
           <t>TEMIRGALIEV Djanibek</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>68797</t>
         </is>
@@ -4359,7 +4389,7 @@
           <t>MING Xingzhou</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>146482</t>
         </is>
@@ -4422,7 +4452,7 @@
           <t>MAPELLI Guilherme</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -4485,7 +4515,7 @@
           <t>BARAT Andy</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>129965</t>
         </is>
@@ -4548,7 +4578,7 @@
           <t>MARTINEZ Jesus</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>118831</t>
         </is>
@@ -4611,7 +4641,7 @@
           <t>ZIELONKA Mark</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>89531</t>
         </is>
@@ -4674,7 +4704,7 @@
           <t>CHRISTIE-WILLIAMS John Coleman</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>106170</t>
         </is>
@@ -4737,7 +4767,7 @@
           <t>DORDEVIC Marko</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>87744</t>
         </is>
@@ -4800,7 +4830,7 @@
           <t>ZEITLHOFER Simon</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>105457</t>
         </is>
@@ -4863,7 +4893,7 @@
           <t>BOYD Trevor</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>71799</t>
         </is>
@@ -4926,7 +4956,7 @@
           <t>HUANG Liman</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
@@ -4989,7 +5019,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -5052,7 +5082,7 @@
           <t>BROWN Jake</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>86247</t>
         </is>
@@ -5115,7 +5145,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -5178,7 +5208,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -5241,7 +5271,7 @@
           <t>WU Shao-Hsuan</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>43104</t>
         </is>
@@ -5304,7 +5334,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -5367,7 +5397,7 @@
           <t>COLLIER Nicholas</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>93695</t>
         </is>
@@ -5430,7 +5460,7 @@
           <t>LONG Kyler James</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>106175</t>
         </is>
@@ -5493,7 +5523,7 @@
           <t>VERNON Reilly</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>130120</t>
         </is>
@@ -5556,7 +5586,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -5619,7 +5649,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -5682,7 +5712,7 @@
           <t>JACOB Lucas</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>106067</t>
         </is>
@@ -5745,7 +5775,7 @@
           <t>BARTA Jan</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>75448</t>
         </is>
@@ -5808,7 +5838,7 @@
           <t>GONSENICA Adam</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>55165</t>
         </is>
@@ -5871,7 +5901,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -5934,7 +5964,7 @@
           <t>MARX Dimitri</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>60326</t>
         </is>
@@ -5997,7 +6027,7 @@
           <t>VALANT Ulan</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>83908</t>
         </is>
@@ -6060,7 +6090,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -6123,7 +6153,7 @@
           <t>AUBERTIN Maxime</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>104390</t>
         </is>
@@ -6186,7 +6216,7 @@
           <t>BRZEZINSKI Jakub</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>43977</t>
         </is>
@@ -6249,7 +6279,7 @@
           <t>TANAKA Yuuki</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>75422</t>
         </is>
@@ -6312,7 +6342,7 @@
           <t>MUTO Yusuke</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>71820</t>
         </is>
@@ -6375,7 +6405,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -6438,7 +6468,7 @@
           <t>HAYLETT Ben</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>69122</t>
         </is>
@@ -6501,7 +6531,7 @@
           <t>PISTONI Michele</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>105983</t>
         </is>
@@ -6564,7 +6594,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -6627,7 +6657,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -6690,7 +6720,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -6753,7 +6783,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -6816,7 +6846,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -6879,7 +6909,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -6942,7 +6972,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -7005,7 +7035,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -7068,7 +7098,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -7131,7 +7161,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -7194,7 +7224,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -7257,7 +7287,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -7320,7 +7350,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -7383,7 +7413,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -7446,7 +7476,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -7509,7 +7539,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -7572,7 +7602,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -7635,7 +7665,7 @@
           <t>HOCEVAR Ziga Lin</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>118698</t>
         </is>
@@ -7698,7 +7728,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -7761,7 +7791,7 @@
           <t>FERRAZZI Xabier</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>105988</t>
         </is>
@@ -7824,7 +7854,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -7887,7 +7917,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -7950,7 +7980,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -8013,7 +8043,7 @@
           <t>KREJCI Jakub</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>83510</t>
         </is>
@@ -8076,7 +8106,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -8139,7 +8169,7 @@
           <t>DELASSUS Anatole</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>84109</t>
         </is>
@@ -8202,7 +8232,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -8265,7 +8295,7 @@
           <t>CASTRYCK Titouan</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>88701</t>
         </is>
@@ -8328,7 +8358,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -8391,7 +8421,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -8454,7 +8484,7 @@
           <t>YANG Ting</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>146484</t>
         </is>
@@ -8517,7 +8547,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>118428</t>
         </is>
@@ -8580,7 +8610,7 @@
           <t>XU Jiaqi</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>142190</t>
         </is>
@@ -8643,7 +8673,7 @@
           <t>WU Yishan</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>130289</t>
         </is>
@@ -8706,7 +8736,7 @@
           <t>MASSARENTI Carolina</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>142089</t>
         </is>
@@ -8769,7 +8799,7 @@
           <t>ALTMAN Marcella</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>97011</t>
         </is>
@@ -8832,7 +8862,7 @@
           <t>CORCORAN Michaela</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>106164</t>
         </is>
@@ -8895,7 +8925,7 @@
           <t>MORENOVA Adriana</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>98979</t>
         </is>
@@ -8958,7 +8988,7 @@
           <t>GORA Aleksandra</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -9021,7 +9051,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -9084,7 +9114,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -9147,7 +9177,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -9210,7 +9240,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -9273,7 +9303,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -9336,7 +9366,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -9399,7 +9429,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -9462,7 +9492,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -9525,7 +9555,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -9588,7 +9618,7 @@
           <t>MILLER Ellis</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>75828</t>
         </is>
@@ -9651,7 +9681,7 @@
           <t>DELASSUS Doriane</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>84178</t>
         </is>
@@ -9714,7 +9744,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -9777,7 +9807,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -9840,7 +9870,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -9903,7 +9933,7 @@
           <t>BERTONCELLI Marta</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>71982</t>
         </is>
@@ -9966,7 +9996,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -10029,7 +10059,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -10092,7 +10122,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -10155,7 +10185,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -10218,7 +10248,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -10281,7 +10311,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -10344,7 +10374,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -10407,7 +10437,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -10470,7 +10500,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -10533,7 +10563,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -10596,7 +10626,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -10659,7 +10689,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -10722,7 +10752,7 @@
           <t>SATKOVA Gabriela</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>68786</t>
         </is>
@@ -10785,7 +10815,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -10848,7 +10878,7 @@
           <t>SHEN Yufei</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>146476</t>
         </is>
@@ -10911,7 +10941,7 @@
           <t>KURBANALIEV Sherzod</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>112912</t>
         </is>
@@ -10974,7 +11004,7 @@
           <t>ZHANG Zhicheng</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>63800</t>
         </is>
@@ -11037,7 +11067,7 @@
           <t>ROZENTALS Klass Francisks</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>142203</t>
         </is>
@@ -11100,7 +11130,7 @@
           <t>ELLIS Declan</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>93769</t>
         </is>
@@ -11163,7 +11193,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -11226,7 +11256,7 @@
           <t>KLEVLEEV Anvar</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>130188</t>
         </is>
@@ -11289,7 +11319,7 @@
           <t>ZIMMERMANN Niels</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>112606</t>
         </is>
@@ -11352,7 +11382,7 @@
           <t>ROYLE Luc</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>97349</t>
         </is>
@@ -11415,7 +11445,7 @@
           <t>WIERCIOCH Michal</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
@@ -11478,7 +11508,7 @@
           <t>ZHANG Peng</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>63799</t>
         </is>
@@ -11541,7 +11571,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -11604,7 +11634,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -11667,7 +11697,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -11730,7 +11760,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -11793,7 +11823,7 @@
           <t>PUCHNER Oliver</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>83529</t>
         </is>
@@ -11856,7 +11886,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -11919,7 +11949,7 @@
           <t>VICENTE Marc</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>106068</t>
         </is>
@@ -11982,7 +12012,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -12045,7 +12075,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -12108,7 +12138,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -12171,7 +12201,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -12234,7 +12264,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -12297,7 +12327,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -12360,7 +12390,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -12423,7 +12453,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -12486,7 +12516,7 @@
           <t>TUCHSCHERER Lennard</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
@@ -12549,7 +12579,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -12612,7 +12642,7 @@
           <t>BASSETT Kaylen</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>75376</t>
         </is>
@@ -12675,7 +12705,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -12738,7 +12768,7 @@
           <t>KRAL Adam</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>83772</t>
         </is>
@@ -12801,7 +12831,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -12864,7 +12894,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -12927,7 +12957,7 @@
           <t>MICOZZI Flavio</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>77363</t>
         </is>
@@ -12990,7 +13020,7 @@
           <t>BARZON Martino</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>83978</t>
         </is>
@@ -13053,7 +13083,7 @@
           <t>DEBLIQUY Mewen</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>88656</t>
         </is>
@@ -13116,7 +13146,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -13179,7 +13209,7 @@
           <t>SENECHAULT Yohann</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>84177</t>
         </is>
@@ -13242,7 +13272,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -13305,7 +13335,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -13368,7 +13398,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -13431,7 +13461,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -13494,7 +13524,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -13557,7 +13587,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -13620,7 +13650,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -13683,7 +13713,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -13746,7 +13776,7 @@
           <t>HOCEVAR Ziga Lin</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>118698</t>
         </is>
@@ -13809,7 +13839,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -13872,7 +13902,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -13935,7 +13965,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -14008,7 +14038,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -14081,7 +14111,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -14154,7 +14184,7 @@
           <t>APEL Emily</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>83788</t>
         </is>
@@ -14227,7 +14257,7 @@
           <t>SETCHELL Nikita</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>86250</t>
         </is>
@@ -14300,7 +14330,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -14373,7 +14403,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -14446,7 +14476,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -14519,7 +14549,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -14592,7 +14622,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -14665,7 +14695,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -14738,7 +14768,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -14811,7 +14841,7 @@
           <t>SATKOVA Gabriela</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>68786</t>
         </is>
@@ -14884,7 +14914,7 @@
           <t>TANAKA Yuuki</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>75422</t>
         </is>
@@ -14957,7 +14987,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -15030,7 +15060,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -15103,7 +15133,7 @@
           <t>GONSENICA Adam</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>55165</t>
         </is>
@@ -15176,7 +15206,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -15249,7 +15279,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -15322,7 +15352,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -15395,7 +15425,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -15468,7 +15498,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -15541,7 +15571,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -15614,7 +15644,7 @@
           <t>BARTA Jan</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>75448</t>
         </is>
@@ -15687,7 +15717,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -15760,7 +15790,7 @@
           <t>WU Yishan</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>130289</t>
         </is>
@@ -15833,7 +15863,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -15906,7 +15936,7 @@
           <t>GORA Aleksandra</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -15979,7 +16009,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -16052,7 +16082,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -16125,7 +16155,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -16198,7 +16228,7 @@
           <t>BERTONCELLI Marta</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>71982</t>
         </is>
@@ -16271,7 +16301,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -16344,7 +16374,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -16417,7 +16447,7 @@
           <t>DELASSUS Doriane</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>84178</t>
         </is>
@@ -16490,7 +16520,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -16563,7 +16593,7 @@
           <t>SATKOVA Gabriela</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>68786</t>
         </is>
@@ -16636,7 +16666,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -16709,7 +16739,7 @@
           <t>KRAL Adam</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>83772</t>
         </is>
@@ -16782,7 +16812,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -16855,7 +16885,7 @@
           <t>DEBLIQUY Mewen</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>88656</t>
         </is>
@@ -16928,7 +16958,7 @@
           <t>HOCEVAR Ziga Lin</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>118698</t>
         </is>
@@ -17001,7 +17031,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -17074,7 +17104,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -17147,7 +17177,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -17220,7 +17250,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -17293,7 +17323,7 @@
           <t>SENECHAULT Yohann</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>84177</t>
         </is>
@@ -17366,7 +17396,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -17439,7 +17469,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -18305,7 +18335,7 @@
           <t>YANG Ting</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>146484</t>
         </is>
@@ -18363,7 +18393,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>118428</t>
         </is>
@@ -18421,7 +18451,7 @@
           <t>XU Jiaqi</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>142190</t>
         </is>
@@ -18479,7 +18509,7 @@
           <t>WU Yishan</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>130289</t>
         </is>
@@ -18537,7 +18567,7 @@
           <t>MASSARENTI Carolina</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>142089</t>
         </is>
@@ -18595,7 +18625,7 @@
           <t>ALTMAN Marcella</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>97011</t>
         </is>
@@ -18653,7 +18683,7 @@
           <t>CORCORAN Michaela</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>106164</t>
         </is>
@@ -18711,7 +18741,7 @@
           <t>MORENOVA Adriana</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>98979</t>
         </is>
@@ -18769,7 +18799,7 @@
           <t>GORA Aleksandra</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -18827,7 +18857,7 @@
           <t>FORROW Bethan</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>69065</t>
         </is>
@@ -18885,7 +18915,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -18943,7 +18973,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -19001,7 +19031,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -19059,7 +19089,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -19117,7 +19147,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -19175,7 +19205,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -19233,7 +19263,7 @@
           <t>BORGHI Elena</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>75493</t>
         </is>
@@ -19291,7 +19321,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -19349,7 +19379,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -19407,7 +19437,7 @@
           <t>MILLER Ellis</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>75828</t>
         </is>
@@ -19465,7 +19495,7 @@
           <t>DELASSUS Doriane</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>84178</t>
         </is>
@@ -19523,7 +19553,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -19581,7 +19611,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -19639,7 +19669,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -19697,7 +19727,7 @@
           <t>BERTONCELLI Marta</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>71982</t>
         </is>
@@ -19755,7 +19785,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -19813,7 +19843,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -19871,7 +19901,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -19929,7 +19959,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -19987,7 +20017,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -20045,7 +20075,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -20103,7 +20133,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -20161,7 +20191,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -20219,7 +20249,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -20277,7 +20307,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -20335,7 +20365,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -20393,7 +20423,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -20451,7 +20481,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -20509,7 +20539,7 @@
           <t>SATKOVA Gabriela</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>68786</t>
         </is>
@@ -20567,7 +20597,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -20625,7 +20655,7 @@
           <t>SHEN Yufei</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>146476</t>
         </is>
@@ -20683,7 +20713,7 @@
           <t>KURBANALIEV Sherzod</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>112912</t>
         </is>
@@ -20741,7 +20771,7 @@
           <t>ZHANG Zhicheng</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>63800</t>
         </is>
@@ -20799,7 +20829,7 @@
           <t>ROZENTALS Klass Francisks</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>142203</t>
         </is>
@@ -20857,7 +20887,7 @@
           <t>ELLIS Declan</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>93769</t>
         </is>
@@ -20915,7 +20945,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -20973,7 +21003,7 @@
           <t>KLEVLEEV Anvar</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>130188</t>
         </is>
@@ -21031,7 +21061,7 @@
           <t>ZIMMERMANN Niels</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>112606</t>
         </is>
@@ -21089,7 +21119,7 @@
           <t>ROYLE Luc</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>97349</t>
         </is>
@@ -21147,7 +21177,7 @@
           <t>WIERCIOCH Michal</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
@@ -21205,7 +21235,7 @@
           <t>ZHANG Peng</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>63799</t>
         </is>
@@ -21263,7 +21293,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -21321,7 +21351,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -21379,7 +21409,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -21437,7 +21467,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -21495,7 +21525,7 @@
           <t>PUCHNER Oliver</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>83529</t>
         </is>
@@ -21553,7 +21583,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -21611,7 +21641,7 @@
           <t>VICENTE Marc</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>106068</t>
         </is>
@@ -21669,7 +21699,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -21727,7 +21757,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -21785,7 +21815,7 @@
           <t>HENDRICK Robert</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>43002</t>
         </is>
@@ -21843,7 +21873,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -21901,7 +21931,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -21959,7 +21989,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -22017,7 +22047,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -22075,7 +22105,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -22133,7 +22163,7 @@
           <t>TUCHSCHERER Lennard</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>60090</t>
         </is>
@@ -22191,7 +22221,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -22249,7 +22279,7 @@
           <t>BASSETT Kaylen</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>75376</t>
         </is>
@@ -22307,7 +22337,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -22365,7 +22395,7 @@
           <t>KRAL Adam</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>83772</t>
         </is>
@@ -22423,7 +22453,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -22481,7 +22511,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -22539,7 +22569,7 @@
           <t>MICOZZI Flavio</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>77363</t>
         </is>
@@ -22597,7 +22627,7 @@
           <t>BARZON Martino</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>83978</t>
         </is>
@@ -22655,7 +22685,7 @@
           <t>DEBLIQUY Mewen</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>88656</t>
         </is>
@@ -22713,7 +22743,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -22771,7 +22801,7 @@
           <t>SENECHAULT Yohann</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>84177</t>
         </is>
@@ -22829,7 +22859,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -22887,7 +22917,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -22945,7 +22975,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -23003,7 +23033,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -23061,7 +23091,7 @@
           <t>MIRGORODSKY Marko</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>42019</t>
         </is>
@@ -23119,7 +23149,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -23177,7 +23207,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -23235,7 +23265,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -23293,7 +23323,7 @@
           <t>HOCEVAR Ziga Lin</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>118698</t>
         </is>
@@ -23351,7 +23381,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -23409,7 +23439,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -23467,7 +23497,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -23535,7 +23565,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -23603,7 +23633,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -23671,7 +23701,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -23739,7 +23769,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -23807,7 +23837,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -23875,7 +23905,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -23943,7 +23973,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -24011,7 +24041,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -24079,7 +24109,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -24147,7 +24177,7 @@
           <t>SATKOVA Gabriela</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>68786</t>
         </is>
@@ -24215,7 +24245,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -24283,7 +24313,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -24351,7 +24381,7 @@
           <t>KRAL Adam</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>83772</t>
         </is>
@@ -24419,7 +24449,7 @@
           <t>BASSETT Kaylen</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>75376</t>
         </is>
@@ -24487,7 +24517,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -24555,7 +24585,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -24623,7 +24653,7 @@
           <t>GESTIN Nicolas</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>71961</t>
         </is>
@@ -24691,7 +24721,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -24759,7 +24789,7 @@
           <t>BARZON Martino</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>83978</t>
         </is>
@@ -24827,7 +24857,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -24895,7 +24925,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -24963,7 +24993,7 @@
           <t>SENECHAULT Yohann</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>84177</t>
         </is>
@@ -25031,7 +25061,7 @@
           <t>HOCEVAR Ziga Lin</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>118698</t>
         </is>
@@ -25099,7 +25129,7 @@
           <t>DEBLIQUY Mewen</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>88656</t>
         </is>
@@ -25157,7 +25187,7 @@
           <t>WOOD Emmi</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>154168</t>
         </is>
@@ -25215,7 +25245,7 @@
           <t>MILLS Waris</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>154167</t>
         </is>
@@ -25273,7 +25303,7 @@
           <t>CHEN Lin</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>87704</t>
         </is>
@@ -25331,7 +25361,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -25389,7 +25419,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -25447,7 +25477,7 @@
           <t>XIE Xueting</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>130285</t>
         </is>
@@ -25505,7 +25535,7 @@
           <t>WAN Shunfang</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>118852</t>
         </is>
@@ -25563,7 +25593,7 @@
           <t>ALTMAN Marcella</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>97011</t>
         </is>
@@ -25621,7 +25651,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -25679,7 +25709,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -25737,7 +25767,7 @@
           <t>CHANG Chu-Han</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>51896</t>
         </is>
@@ -25795,7 +25825,7 @@
           <t>NOVAK Lea</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>60323</t>
         </is>
@@ -25853,7 +25883,7 @@
           <t>SETCHELL Nikita</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>86250</t>
         </is>
@@ -25911,7 +25941,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>118428</t>
         </is>
@@ -25969,7 +25999,7 @@
           <t>GONI Leire</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>93966</t>
         </is>
@@ -26027,7 +26057,7 @@
           <t>APEL Emily</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>83788</t>
         </is>
@@ -26085,7 +26115,7 @@
           <t>PIETRACHA Eva</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>84043</t>
         </is>
@@ -26143,7 +26173,7 @@
           <t>NESNIDALOVA Lucie</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>75449</t>
         </is>
@@ -26201,7 +26231,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -26259,7 +26289,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -26317,7 +26347,7 @@
           <t>SRIBAR Ria</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>75645</t>
         </is>
@@ -26375,7 +26405,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -26433,7 +26463,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -26491,7 +26521,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -26549,7 +26579,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -26607,7 +26637,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -26665,7 +26695,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -26723,7 +26753,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -26781,7 +26811,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -26839,7 +26869,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -26897,7 +26927,7 @@
           <t>GALUSKOVA Antonie</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>68754</t>
         </is>
@@ -26955,7 +26985,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -27013,7 +27043,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -27071,7 +27101,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -27129,7 +27159,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -27187,7 +27217,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -27245,7 +27275,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -27303,7 +27333,7 @@
           <t>SATKOVA Gabriela</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>68786</t>
         </is>
@@ -27361,7 +27391,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -27419,7 +27449,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -27477,7 +27507,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -27535,7 +27565,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -27593,7 +27623,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -27651,7 +27681,7 @@
           <t>RAW Brayden</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>154169</t>
         </is>
@@ -27709,7 +27739,7 @@
           <t>VAN HEERDEN Matthew</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>143591</t>
         </is>
@@ -27767,7 +27797,7 @@
           <t>ZHANG Hejie</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>130284</t>
         </is>
@@ -27825,7 +27855,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>153722</t>
         </is>
@@ -27883,7 +27913,7 @@
           <t>PARK Moorim</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>100009</t>
         </is>
@@ -27941,7 +27971,7 @@
           <t>MAGAN Raage</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>141057</t>
         </is>
@@ -27999,7 +28029,7 @@
           <t>MAGAN Aar</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>141058</t>
         </is>
@@ -28057,7 +28087,7 @@
           <t>TEMIRGALIEV Djanibek</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>68797</t>
         </is>
@@ -28115,7 +28145,7 @@
           <t>MING Xingzhou</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>146482</t>
         </is>
@@ -28173,7 +28203,7 @@
           <t>MAPELLI Guilherme</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -28231,7 +28261,7 @@
           <t>BARAT Andy</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>129965</t>
         </is>
@@ -28289,7 +28319,7 @@
           <t>MARTINEZ Jesus</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>118831</t>
         </is>
@@ -28347,7 +28377,7 @@
           <t>ZIELONKA Mark</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>89531</t>
         </is>
@@ -28405,7 +28435,7 @@
           <t>CHRISTIE-WILLIAMS John Coleman</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>106170</t>
         </is>
@@ -28463,7 +28493,7 @@
           <t>DORDEVIC Marko</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>87744</t>
         </is>
@@ -28521,7 +28551,7 @@
           <t>ZEITLHOFER Simon</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>105457</t>
         </is>
@@ -28579,7 +28609,7 @@
           <t>BOYD Trevor</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>71799</t>
         </is>
@@ -28637,7 +28667,7 @@
           <t>HUANG Liman</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
@@ -28695,7 +28725,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -28753,7 +28783,7 @@
           <t>BROWN Jake</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>86247</t>
         </is>
@@ -28811,7 +28841,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -28869,7 +28899,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -28927,7 +28957,7 @@
           <t>WU Shao-Hsuan</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>43104</t>
         </is>
@@ -28985,7 +29015,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -29043,7 +29073,7 @@
           <t>COLLIER Nicholas</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>93695</t>
         </is>
@@ -29101,7 +29131,7 @@
           <t>LONG Kyler James</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>106175</t>
         </is>
@@ -29159,7 +29189,7 @@
           <t>VERNON Reilly</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>130120</t>
         </is>
@@ -29217,7 +29247,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -29275,7 +29305,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -29333,7 +29363,7 @@
           <t>JACOB Lucas</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>106067</t>
         </is>
@@ -29391,7 +29421,7 @@
           <t>BARTA Jan</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>75448</t>
         </is>
@@ -29449,7 +29479,7 @@
           <t>GONSENICA Adam</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>55165</t>
         </is>
@@ -29507,7 +29537,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -29565,7 +29595,7 @@
           <t>MARX Dimitri</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>60326</t>
         </is>
@@ -29623,7 +29653,7 @@
           <t>VALANT Ulan</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>83908</t>
         </is>
@@ -29681,7 +29711,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -29739,7 +29769,7 @@
           <t>AUBERTIN Maxime</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>104390</t>
         </is>
@@ -29797,7 +29827,7 @@
           <t>BRZEZINSKI Jakub</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>43977</t>
         </is>
@@ -29855,7 +29885,7 @@
           <t>TANAKA Yuuki</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>75422</t>
         </is>
@@ -29913,7 +29943,7 @@
           <t>MUTO Yusuke</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>71820</t>
         </is>
@@ -29971,7 +30001,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -30029,7 +30059,7 @@
           <t>HAYLETT Ben</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>69122</t>
         </is>
@@ -30087,7 +30117,7 @@
           <t>PISTONI Michele</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>105983</t>
         </is>
@@ -30145,7 +30175,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -30203,7 +30233,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -30261,7 +30291,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -30319,7 +30349,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -30377,7 +30407,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -30435,7 +30465,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -30493,7 +30523,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -30551,7 +30581,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -30609,7 +30639,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -30667,7 +30697,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -30725,7 +30755,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -30783,7 +30813,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -30841,7 +30871,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -30899,7 +30929,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -30957,7 +30987,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -31015,7 +31045,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -31073,7 +31103,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -31131,7 +31161,7 @@
           <t>HOCEVAR Ziga Lin</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>118698</t>
         </is>
@@ -31189,7 +31219,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -31247,7 +31277,7 @@
           <t>FERRAZZI Xabier</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>105988</t>
         </is>
@@ -31305,7 +31335,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -31363,7 +31393,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -31421,7 +31451,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -31479,7 +31509,7 @@
           <t>KREJCI Jakub</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>83510</t>
         </is>
@@ -31537,7 +31567,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -31595,7 +31625,7 @@
           <t>DELASSUS Anatole</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>84109</t>
         </is>
@@ -31653,7 +31683,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -31711,7 +31741,7 @@
           <t>CASTRYCK Titouan</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>88701</t>
         </is>
@@ -31769,7 +31799,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -31827,7 +31857,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -31895,7 +31925,7 @@
           <t>GONI Leire</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>93966</t>
         </is>
@@ -31963,7 +31993,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -32031,7 +32061,7 @@
           <t>GALUSKOVA Antonie</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>68754</t>
         </is>
@@ -32099,7 +32129,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -32167,7 +32197,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -32235,7 +32265,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -32303,7 +32333,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -32371,7 +32401,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -32439,7 +32469,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -32507,7 +32537,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -32575,7 +32605,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -32643,7 +32673,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -32711,7 +32741,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -32779,7 +32809,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -32847,7 +32877,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -32915,7 +32945,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -32983,7 +33013,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -33051,7 +33081,7 @@
           <t>CASTRYCK Titouan</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>88701</t>
         </is>
@@ -33119,7 +33149,7 @@
           <t>DELASSUS Anatole</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>84109</t>
         </is>
@@ -33187,7 +33217,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -33255,7 +33285,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -33323,7 +33353,7 @@
           <t>HAYLETT Ben</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>69122</t>
         </is>
@@ -33391,7 +33421,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -33459,7 +33489,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -33754,7 +33784,7 @@
           <t>MILLS Waris</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>154167</t>
         </is>
@@ -33817,7 +33847,7 @@
           <t>WOOD Emmi</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>154168</t>
         </is>
@@ -33880,7 +33910,7 @@
           <t>LUKNAROVA Emanuela</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>76973</t>
         </is>
@@ -33943,7 +33973,7 @@
           <t>CHEN Lin</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>87704</t>
         </is>
@@ -34006,7 +34036,7 @@
           <t>NESNIDALOVA Lucie</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>75449</t>
         </is>
@@ -34069,7 +34099,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -34132,7 +34162,7 @@
           <t>PITCHER FARRELL Cleo</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>106358</t>
         </is>
@@ -34195,7 +34225,7 @@
           <t>WAN Shunfang</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>118852</t>
         </is>
@@ -34258,7 +34288,7 @@
           <t>SAMKOVA Olga</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>105999</t>
         </is>
@@ -34321,7 +34351,7 @@
           <t>GORA Aleksandra</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>61261</t>
         </is>
@@ -34384,7 +34414,7 @@
           <t>PLATA Laura</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>141991</t>
         </is>
@@ -34447,7 +34477,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -34510,7 +34540,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -34573,7 +34603,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -34636,7 +34666,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -34699,7 +34729,7 @@
           <t>ALTMAN Marcella</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>97011</t>
         </is>
@@ -34762,7 +34792,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -34825,7 +34855,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -34888,7 +34918,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -34951,7 +34981,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -35014,7 +35044,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -35077,7 +35107,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -35140,7 +35170,7 @@
           <t>PINTERIC Naja</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>106223</t>
         </is>
@@ -35203,7 +35233,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>118428</t>
         </is>
@@ -35266,7 +35296,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -35329,7 +35359,7 @@
           <t>XIE Xueting</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>130285</t>
         </is>
@@ -35392,7 +35422,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -35455,7 +35485,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -35518,7 +35548,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -35581,7 +35611,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -35644,7 +35674,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -35707,7 +35737,7 @@
           <t>SETCHELL Nikita</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>86250</t>
         </is>
@@ -35770,7 +35800,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -35833,7 +35863,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -35896,7 +35926,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -35959,7 +35989,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -36022,7 +36052,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -36085,7 +36115,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -36148,7 +36178,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -36211,7 +36241,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -36274,7 +36304,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -36337,7 +36367,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -36400,7 +36430,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>153722</t>
         </is>
@@ -36463,7 +36493,7 @@
           <t>RAW Brayden</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>154169</t>
         </is>
@@ -36526,7 +36556,7 @@
           <t>VAN HEERDEN Matthew</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>143591</t>
         </is>
@@ -36589,7 +36619,7 @@
           <t>MUTO Yusuke</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>71820</t>
         </is>
@@ -36652,7 +36682,7 @@
           <t>TEMIRGALIEV Djanibek</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>68797</t>
         </is>
@@ -36715,7 +36745,7 @@
           <t>MING Xingzhou</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>146482</t>
         </is>
@@ -36778,7 +36808,7 @@
           <t>MAPELLI Guilherme</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -36841,7 +36871,7 @@
           <t>ZHANG Hejie</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>130284</t>
         </is>
@@ -36904,7 +36934,7 @@
           <t>RUDORFER Martin</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>83774</t>
         </is>
@@ -36967,7 +36997,7 @@
           <t>GONSENICA Adam</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>55165</t>
         </is>
@@ -37030,7 +37060,7 @@
           <t>MAGAN Raage</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>141057</t>
         </is>
@@ -37093,7 +37123,7 @@
           <t>MAGAN Aar</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>141058</t>
         </is>
@@ -37156,7 +37186,7 @@
           <t>TANAKA Yuuki</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>75422</t>
         </is>
@@ -37219,7 +37249,7 @@
           <t>ZEITLHOFER Simon</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>105457</t>
         </is>
@@ -37282,7 +37312,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -37345,7 +37375,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -37408,7 +37438,7 @@
           <t>ROZENTALS Klass Francisks</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>142203</t>
         </is>
@@ -37471,7 +37501,7 @@
           <t>BARAT Andy</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>129965</t>
         </is>
@@ -37534,7 +37564,7 @@
           <t>JACOB Lucas</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>106067</t>
         </is>
@@ -37597,7 +37627,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -37660,7 +37690,7 @@
           <t>HUANG Liman</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
@@ -37723,7 +37753,7 @@
           <t>ZIELONKA Mark</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
+      <c r="X603" t="inlineStr">
         <is>
           <t>89531</t>
         </is>
@@ -37786,7 +37816,7 @@
           <t>BOYD Trevor</t>
         </is>
       </c>
-      <c r="U604" t="inlineStr">
+      <c r="X604" t="inlineStr">
         <is>
           <t>71799</t>
         </is>
@@ -37849,7 +37879,7 @@
           <t>PUCHNER Oliver</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>83529</t>
         </is>
@@ -37912,7 +37942,7 @@
           <t>TRIPANO Manuel</t>
         </is>
       </c>
-      <c r="U606" t="inlineStr">
+      <c r="X606" t="inlineStr">
         <is>
           <t>93235</t>
         </is>
@@ -37975,7 +38005,7 @@
           <t>BRZEZINSKI Jakub</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>43977</t>
         </is>
@@ -38038,7 +38068,7 @@
           <t>ECHANIZ Pau</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>75786</t>
         </is>
@@ -38101,7 +38131,7 @@
           <t>FERRAZZI Xabier</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>105988</t>
         </is>
@@ -38164,7 +38194,7 @@
           <t>AUBERTIN Maxime</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
+      <c r="X610" t="inlineStr">
         <is>
           <t>104390</t>
         </is>
@@ -38227,7 +38257,7 @@
           <t>NOVAK Matyas</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>105998</t>
         </is>
@@ -38290,7 +38320,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -38353,7 +38383,7 @@
           <t>MARTINEZ Jesus</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>118831</t>
         </is>
@@ -38416,7 +38446,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -38479,7 +38509,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U615" t="inlineStr">
+      <c r="X615" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -38542,7 +38572,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U616" t="inlineStr">
+      <c r="X616" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -38605,7 +38635,7 @@
           <t>COLLIER Nicholas</t>
         </is>
       </c>
-      <c r="U617" t="inlineStr">
+      <c r="X617" t="inlineStr">
         <is>
           <t>93695</t>
         </is>
@@ -38668,7 +38698,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U618" t="inlineStr">
+      <c r="X618" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -38731,7 +38761,7 @@
           <t>ROELLER Tillmann</t>
         </is>
       </c>
-      <c r="U619" t="inlineStr">
+      <c r="X619" t="inlineStr">
         <is>
           <t>83990</t>
         </is>
@@ -38794,7 +38824,7 @@
           <t>KANCLER Tine</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>51813</t>
         </is>
@@ -38857,7 +38887,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -38920,7 +38950,7 @@
           <t>LONG Kyler James</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>106175</t>
         </is>
@@ -38983,7 +39013,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -39046,7 +39076,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -39109,7 +39139,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -39172,7 +39202,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -39235,7 +39265,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -39298,7 +39328,7 @@
           <t>KREJCI Jakub</t>
         </is>
       </c>
-      <c r="U628" t="inlineStr">
+      <c r="X628" t="inlineStr">
         <is>
           <t>83510</t>
         </is>
@@ -39361,7 +39391,7 @@
           <t>HOCEVAR Ziga Lin</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>118698</t>
         </is>
@@ -39424,7 +39454,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U630" t="inlineStr">
+      <c r="X630" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -39487,7 +39517,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U631" t="inlineStr">
+      <c r="X631" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -39550,7 +39580,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -39613,7 +39643,7 @@
           <t>CASTRYCK Titouan</t>
         </is>
       </c>
-      <c r="U633" t="inlineStr">
+      <c r="X633" t="inlineStr">
         <is>
           <t>88701</t>
         </is>
@@ -39676,7 +39706,7 @@
           <t>LEAVER Sam</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>97449</t>
         </is>
@@ -39739,7 +39769,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U635" t="inlineStr">
+      <c r="X635" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -39802,7 +39832,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -39865,7 +39895,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -39928,7 +39958,7 @@
           <t>ROHRER Jan</t>
         </is>
       </c>
-      <c r="U638" t="inlineStr">
+      <c r="X638" t="inlineStr">
         <is>
           <t>68846</t>
         </is>
@@ -39991,7 +40021,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -40054,7 +40084,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U640" t="inlineStr">
+      <c r="X640" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -40117,7 +40147,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -40180,7 +40210,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U642" t="inlineStr">
+      <c r="X642" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -40243,7 +40273,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U643" t="inlineStr">
+      <c r="X643" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -40306,7 +40336,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U644" t="inlineStr">
+      <c r="X644" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -40369,7 +40399,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U645" t="inlineStr">
+      <c r="X645" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -40432,7 +40462,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U646" t="inlineStr">
+      <c r="X646" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -40495,7 +40525,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U647" t="inlineStr">
+      <c r="X647" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -40558,7 +40588,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U648" t="inlineStr">
+      <c r="X648" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -40621,7 +40651,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U649" t="inlineStr">
+      <c r="X649" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -40689,7 +40719,7 @@
           <t>LILIK Elena</t>
         </is>
       </c>
-      <c r="U650" t="inlineStr">
+      <c r="X650" t="inlineStr">
         <is>
           <t>51837</t>
         </is>
@@ -40757,7 +40787,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U651" t="inlineStr">
+      <c r="X651" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -40825,7 +40855,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U652" t="inlineStr">
+      <c r="X652" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -40893,7 +40923,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U653" t="inlineStr">
+      <c r="X653" t="inlineStr">
         <is>
           <t>118428</t>
         </is>
@@ -40961,7 +40991,7 @@
           <t>MARX Alena</t>
         </is>
       </c>
-      <c r="U654" t="inlineStr">
+      <c r="X654" t="inlineStr">
         <is>
           <t>68844</t>
         </is>
@@ -41029,7 +41059,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U655" t="inlineStr">
+      <c r="X655" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -41097,7 +41127,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U656" t="inlineStr">
+      <c r="X656" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -41165,7 +41195,7 @@
           <t>PINTERIC Naja</t>
         </is>
       </c>
-      <c r="U657" t="inlineStr">
+      <c r="X657" t="inlineStr">
         <is>
           <t>106223</t>
         </is>
@@ -41233,7 +41263,7 @@
           <t>XIE Xueting</t>
         </is>
       </c>
-      <c r="U658" t="inlineStr">
+      <c r="X658" t="inlineStr">
         <is>
           <t>130285</t>
         </is>
@@ -41301,7 +41331,7 @@
           <t>PANKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U659" t="inlineStr">
+      <c r="X659" t="inlineStr">
         <is>
           <t>93906</t>
         </is>
@@ -41369,7 +41399,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U660" t="inlineStr">
+      <c r="X660" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -41437,7 +41467,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U661" t="inlineStr">
+      <c r="X661" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -41505,7 +41535,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U662" t="inlineStr">
+      <c r="X662" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -41573,7 +41603,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U663" t="inlineStr">
+      <c r="X663" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -41641,7 +41671,7 @@
           <t>SAMKOVA Olga</t>
         </is>
       </c>
-      <c r="U664" t="inlineStr">
+      <c r="X664" t="inlineStr">
         <is>
           <t>105999</t>
         </is>
@@ -41709,7 +41739,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U665" t="inlineStr">
+      <c r="X665" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -41777,7 +41807,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U666" t="inlineStr">
+      <c r="X666" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -41845,7 +41875,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U667" t="inlineStr">
+      <c r="X667" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -41913,7 +41943,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U668" t="inlineStr">
+      <c r="X668" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -41981,7 +42011,7 @@
           <t>WAN Shunfang</t>
         </is>
       </c>
-      <c r="U669" t="inlineStr">
+      <c r="X669" t="inlineStr">
         <is>
           <t>118852</t>
         </is>
@@ -42049,7 +42079,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U670" t="inlineStr">
+      <c r="X670" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -42117,7 +42147,7 @@
           <t>VUITTON Emma</t>
         </is>
       </c>
-      <c r="U671" t="inlineStr">
+      <c r="X671" t="inlineStr">
         <is>
           <t>84126</t>
         </is>
@@ -42185,7 +42215,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U672" t="inlineStr">
+      <c r="X672" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -42253,7 +42283,7 @@
           <t>NESNIDALOVA Lucie</t>
         </is>
       </c>
-      <c r="U673" t="inlineStr">
+      <c r="X673" t="inlineStr">
         <is>
           <t>75449</t>
         </is>
@@ -42321,7 +42351,7 @@
           <t>SETCHELL Nikita</t>
         </is>
       </c>
-      <c r="U674" t="inlineStr">
+      <c r="X674" t="inlineStr">
         <is>
           <t>86250</t>
         </is>
@@ -42389,7 +42419,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U675" t="inlineStr">
+      <c r="X675" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -42457,7 +42487,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U676" t="inlineStr">
+      <c r="X676" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -42525,7 +42555,7 @@
           <t>CHEN Lin</t>
         </is>
       </c>
-      <c r="U677" t="inlineStr">
+      <c r="X677" t="inlineStr">
         <is>
           <t>87704</t>
         </is>
@@ -42593,7 +42623,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U678" t="inlineStr">
+      <c r="X678" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -42661,7 +42691,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U679" t="inlineStr">
+      <c r="X679" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -42729,7 +42759,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U680" t="inlineStr">
+      <c r="X680" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -42797,7 +42827,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U681" t="inlineStr">
+      <c r="X681" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -42865,7 +42895,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U682" t="inlineStr">
+      <c r="X682" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -42933,7 +42963,7 @@
           <t>HUANG Liman</t>
         </is>
       </c>
-      <c r="U683" t="inlineStr">
+      <c r="X683" t="inlineStr">
         <is>
           <t>118848</t>
         </is>
@@ -43001,7 +43031,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U684" t="inlineStr">
+      <c r="X684" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -43069,7 +43099,7 @@
           <t>LONG Kyler James</t>
         </is>
       </c>
-      <c r="U685" t="inlineStr">
+      <c r="X685" t="inlineStr">
         <is>
           <t>106175</t>
         </is>
@@ -43137,7 +43167,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U686" t="inlineStr">
+      <c r="X686" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -43205,7 +43235,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U687" t="inlineStr">
+      <c r="X687" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -43273,7 +43303,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U688" t="inlineStr">
+      <c r="X688" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -43341,7 +43371,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U689" t="inlineStr">
+      <c r="X689" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -43409,7 +43439,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U690" t="inlineStr">
+      <c r="X690" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -43477,7 +43507,7 @@
           <t>HOCEVAR Ziga Lin</t>
         </is>
       </c>
-      <c r="U691" t="inlineStr">
+      <c r="X691" t="inlineStr">
         <is>
           <t>118698</t>
         </is>
@@ -43545,7 +43575,7 @@
           <t>CASTRYCK Titouan</t>
         </is>
       </c>
-      <c r="U692" t="inlineStr">
+      <c r="X692" t="inlineStr">
         <is>
           <t>88701</t>
         </is>
@@ -43613,7 +43643,7 @@
           <t>ROELLER Tillmann</t>
         </is>
       </c>
-      <c r="U693" t="inlineStr">
+      <c r="X693" t="inlineStr">
         <is>
           <t>83990</t>
         </is>
@@ -43681,7 +43711,7 @@
           <t>FERRAZZI Xabier</t>
         </is>
       </c>
-      <c r="U694" t="inlineStr">
+      <c r="X694" t="inlineStr">
         <is>
           <t>105988</t>
         </is>
@@ -43749,7 +43779,7 @@
           <t>ROHRER Jan</t>
         </is>
       </c>
-      <c r="U695" t="inlineStr">
+      <c r="X695" t="inlineStr">
         <is>
           <t>68846</t>
         </is>
@@ -43817,7 +43847,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U696" t="inlineStr">
+      <c r="X696" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -43885,7 +43915,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U697" t="inlineStr">
+      <c r="X697" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -43953,7 +43983,7 @@
           <t>RUDORFER Martin</t>
         </is>
       </c>
-      <c r="U698" t="inlineStr">
+      <c r="X698" t="inlineStr">
         <is>
           <t>83774</t>
         </is>
@@ -44021,7 +44051,7 @@
           <t>AUBERTIN Maxime</t>
         </is>
       </c>
-      <c r="U699" t="inlineStr">
+      <c r="X699" t="inlineStr">
         <is>
           <t>104390</t>
         </is>
@@ -44089,7 +44119,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U700" t="inlineStr">
+      <c r="X700" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -44157,7 +44187,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U701" t="inlineStr">
+      <c r="X701" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -44225,7 +44255,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U702" t="inlineStr">
+      <c r="X702" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -44293,7 +44323,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U703" t="inlineStr">
+      <c r="X703" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -44361,7 +44391,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U704" t="inlineStr">
+      <c r="X704" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -44429,7 +44459,7 @@
           <t>COLLIER Nicholas</t>
         </is>
       </c>
-      <c r="U705" t="inlineStr">
+      <c r="X705" t="inlineStr">
         <is>
           <t>93695</t>
         </is>
@@ -44497,7 +44527,7 @@
           <t>NOVAK Matyas</t>
         </is>
       </c>
-      <c r="U706" t="inlineStr">
+      <c r="X706" t="inlineStr">
         <is>
           <t>105998</t>
         </is>
@@ -44565,7 +44595,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U707" t="inlineStr">
+      <c r="X707" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -44633,7 +44663,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U708" t="inlineStr">
+      <c r="X708" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -44701,7 +44731,7 @@
           <t>ANDERSON Timothy</t>
         </is>
       </c>
-      <c r="U709" t="inlineStr">
+      <c r="X709" t="inlineStr">
         <is>
           <t>38432</t>
         </is>
@@ -44769,7 +44799,7 @@
           <t>KANCLER Tine</t>
         </is>
       </c>
-      <c r="U710" t="inlineStr">
+      <c r="X710" t="inlineStr">
         <is>
           <t>51813</t>
         </is>
@@ -44837,7 +44867,7 @@
           <t>LEAVER Sam</t>
         </is>
       </c>
-      <c r="U711" t="inlineStr">
+      <c r="X711" t="inlineStr">
         <is>
           <t>97449</t>
         </is>
@@ -44905,7 +44935,7 @@
           <t>KREJCI Jakub</t>
         </is>
       </c>
-      <c r="U712" t="inlineStr">
+      <c r="X712" t="inlineStr">
         <is>
           <t>83510</t>
         </is>
@@ -44973,7 +45003,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U713" t="inlineStr">
+      <c r="X713" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -45041,7 +45071,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U714" t="inlineStr">
+      <c r="X714" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -45109,7 +45139,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U715" t="inlineStr">
+      <c r="X715" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -45177,7 +45207,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U716" t="inlineStr">
+      <c r="X716" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -45245,7 +45275,7 @@
           <t>LEAVER Lois</t>
         </is>
       </c>
-      <c r="U717" t="inlineStr">
+      <c r="X717" t="inlineStr">
         <is>
           <t>83842</t>
         </is>
@@ -45313,7 +45343,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U718" t="inlineStr">
+      <c r="X718" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -45381,7 +45411,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U719" t="inlineStr">
+      <c r="X719" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -45449,7 +45479,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U720" t="inlineStr">
+      <c r="X720" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -45517,7 +45547,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U721" t="inlineStr">
+      <c r="X721" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -45585,7 +45615,7 @@
           <t>STANOVSKA Sona</t>
         </is>
       </c>
-      <c r="U722" t="inlineStr">
+      <c r="X722" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
@@ -45653,7 +45683,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U723" t="inlineStr">
+      <c r="X723" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -45721,7 +45751,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U724" t="inlineStr">
+      <c r="X724" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -45789,7 +45819,7 @@
           <t>DORIA Monica</t>
         </is>
       </c>
-      <c r="U725" t="inlineStr">
+      <c r="X725" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -45857,7 +45887,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U726" t="inlineStr">
+      <c r="X726" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -45925,7 +45955,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U727" t="inlineStr">
+      <c r="X727" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -45993,7 +46023,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U728" t="inlineStr">
+      <c r="X728" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -46061,7 +46091,7 @@
           <t>BAYN Nele</t>
         </is>
       </c>
-      <c r="U729" t="inlineStr">
+      <c r="X729" t="inlineStr">
         <is>
           <t>75442</t>
         </is>
@@ -46129,7 +46159,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U730" t="inlineStr">
+      <c r="X730" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -46197,7 +46227,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U731" t="inlineStr">
+      <c r="X731" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -46265,7 +46295,7 @@
           <t>DE COSTER Gabriel</t>
         </is>
       </c>
-      <c r="U732" t="inlineStr">
+      <c r="X732" t="inlineStr">
         <is>
           <t>68818</t>
         </is>
@@ -46333,7 +46363,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U733" t="inlineStr">
+      <c r="X733" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -46401,7 +46431,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U734" t="inlineStr">
+      <c r="X734" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -46469,7 +46499,7 @@
           <t>ROELLER Tillmann</t>
         </is>
       </c>
-      <c r="U735" t="inlineStr">
+      <c r="X735" t="inlineStr">
         <is>
           <t>83990</t>
         </is>
@@ -46537,7 +46567,7 @@
           <t>ROHRER Jan</t>
         </is>
       </c>
-      <c r="U736" t="inlineStr">
+      <c r="X736" t="inlineStr">
         <is>
           <t>68846</t>
         </is>
@@ -46605,7 +46635,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U737" t="inlineStr">
+      <c r="X737" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -46673,7 +46703,7 @@
           <t>RUDORFER Martin</t>
         </is>
       </c>
-      <c r="U738" t="inlineStr">
+      <c r="X738" t="inlineStr">
         <is>
           <t>83774</t>
         </is>
@@ -46741,7 +46771,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U739" t="inlineStr">
+      <c r="X739" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -46809,7 +46839,7 @@
           <t>MADORE Mathurin</t>
         </is>
       </c>
-      <c r="U740" t="inlineStr">
+      <c r="X740" t="inlineStr">
         <is>
           <t>51994</t>
         </is>
@@ -46877,7 +46907,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U741" t="inlineStr">
+      <c r="X741" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -46945,7 +46975,7 @@
           <t>LEAVER Sam</t>
         </is>
       </c>
-      <c r="U742" t="inlineStr">
+      <c r="X742" t="inlineStr">
         <is>
           <t>97449</t>
         </is>
@@ -47013,7 +47043,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U743" t="inlineStr">
+      <c r="X743" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -47081,7 +47111,7 @@
           <t>HEGGE Noah</t>
         </is>
       </c>
-      <c r="U744" t="inlineStr">
+      <c r="X744" t="inlineStr">
         <is>
           <t>71837</t>
         </is>
@@ -47149,7 +47179,7 @@
           <t>NOVAK Matyas</t>
         </is>
       </c>
-      <c r="U745" t="inlineStr">
+      <c r="X745" t="inlineStr">
         <is>
           <t>105998</t>
         </is>
@@ -47217,7 +47247,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U746" t="inlineStr">
+      <c r="X746" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -47285,7 +47315,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U747" t="inlineStr">
+      <c r="X747" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -47353,7 +47383,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U748" t="inlineStr">
+      <c r="X748" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -47421,7 +47451,7 @@
           <t>HOCEVAR Eva Alina</t>
         </is>
       </c>
-      <c r="U749" t="inlineStr">
+      <c r="X749" t="inlineStr">
         <is>
           <t>75533</t>
         </is>
@@ -47489,7 +47519,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U750" t="inlineStr">
+      <c r="X750" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -47557,7 +47587,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U751" t="inlineStr">
+      <c r="X751" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -47625,7 +47655,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U752" t="inlineStr">
+      <c r="X752" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -47693,7 +47723,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U753" t="inlineStr">
+      <c r="X753" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -47761,7 +47791,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U754" t="inlineStr">
+      <c r="X754" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -47829,7 +47859,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U755" t="inlineStr">
+      <c r="X755" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -47897,7 +47927,7 @@
           <t>ROHRER Jan</t>
         </is>
       </c>
-      <c r="U756" t="inlineStr">
+      <c r="X756" t="inlineStr">
         <is>
           <t>68846</t>
         </is>
@@ -47965,7 +47995,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U757" t="inlineStr">
+      <c r="X757" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -48033,7 +48063,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U758" t="inlineStr">
+      <c r="X758" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -48101,7 +48131,7 @@
           <t>DICKSON Jonny</t>
         </is>
       </c>
-      <c r="U759" t="inlineStr">
+      <c r="X759" t="inlineStr">
         <is>
           <t>75973</t>
         </is>
@@ -48169,7 +48199,7 @@
           <t>RUDORFER Martin</t>
         </is>
       </c>
-      <c r="U760" t="inlineStr">
+      <c r="X760" t="inlineStr">
         <is>
           <t>83774</t>
         </is>
@@ -48237,7 +48267,7 @@
           <t>NOVAK Matyas</t>
         </is>
       </c>
-      <c r="U761" t="inlineStr">
+      <c r="X761" t="inlineStr">
         <is>
           <t>105998</t>
         </is>
@@ -48315,7 +48345,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U762" t="inlineStr">
+      <c r="X762" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -48393,7 +48423,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U763" t="inlineStr">
+      <c r="X763" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -48471,7 +48501,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U764" t="inlineStr">
+      <c r="X764" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -48549,7 +48579,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U765" t="inlineStr">
+      <c r="X765" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -48627,7 +48657,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U766" t="inlineStr">
+      <c r="X766" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -48705,7 +48735,7 @@
           <t>OCHOA Manuel</t>
         </is>
       </c>
-      <c r="U767" t="inlineStr">
+      <c r="X767" t="inlineStr">
         <is>
           <t>69081</t>
         </is>
@@ -48783,7 +48813,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U768" t="inlineStr">
+      <c r="X768" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -48861,7 +48891,7 @@
           <t>RUDORFER Martin</t>
         </is>
       </c>
-      <c r="U769" t="inlineStr">
+      <c r="X769" t="inlineStr">
         <is>
           <t>83774</t>
         </is>

--- a/events/Prague_2025_WC/Prague_2025_WC_start.xlsx
+++ b/events/Prague_2025_WC/Prague_2025_WC_start.xlsx
@@ -33779,6 +33779,11 @@
       <c r="K540" t="n">
         <v>539</v>
       </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="R540" t="inlineStr">
         <is>
           <t>MILLS Waris</t>
@@ -33842,6 +33847,11 @@
       <c r="K541" t="n">
         <v>540</v>
       </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="R541" t="inlineStr">
         <is>
           <t>WOOD Emmi</t>
@@ -33905,6 +33915,11 @@
       <c r="K542" t="n">
         <v>541</v>
       </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="R542" t="inlineStr">
         <is>
           <t>LUKNAROVA Emanuela</t>
@@ -33968,6 +33983,11 @@
       <c r="K543" t="n">
         <v>542</v>
       </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="R543" t="inlineStr">
         <is>
           <t>CHEN Lin</t>
@@ -34031,6 +34051,11 @@
       <c r="K544" t="n">
         <v>543</v>
       </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="R544" t="inlineStr">
         <is>
           <t>NESNIDALOVA Lucie</t>
@@ -34094,6 +34119,11 @@
       <c r="K545" t="n">
         <v>544</v>
       </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="R545" t="inlineStr">
         <is>
           <t>BAYN Nele</t>
@@ -34157,6 +34187,11 @@
       <c r="K546" t="n">
         <v>545</v>
       </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="R546" t="inlineStr">
         <is>
           <t>PITCHER FARRELL Cleo</t>
@@ -34220,6 +34255,11 @@
       <c r="K547" t="n">
         <v>546</v>
       </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="R547" t="inlineStr">
         <is>
           <t>WAN Shunfang</t>
@@ -34283,6 +34323,11 @@
       <c r="K548" t="n">
         <v>547</v>
       </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R548" t="inlineStr">
         <is>
           <t>SAMKOVA Olga</t>
@@ -34346,6 +34391,11 @@
       <c r="K549" t="n">
         <v>548</v>
       </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="R549" t="inlineStr">
         <is>
           <t>GORA Aleksandra</t>
@@ -34472,6 +34522,11 @@
       <c r="K551" t="n">
         <v>550</v>
       </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="R551" t="inlineStr">
         <is>
           <t>SORRIBES Laia</t>
@@ -34535,6 +34590,11 @@
       <c r="K552" t="n">
         <v>551</v>
       </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="R552" t="inlineStr">
         <is>
           <t>WILLIAMS Courtney</t>
@@ -34598,6 +34658,11 @@
       <c r="K553" t="n">
         <v>552</v>
       </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R553" t="inlineStr">
         <is>
           <t>LEAVER Lois</t>
@@ -34661,6 +34726,11 @@
       <c r="K554" t="n">
         <v>553</v>
       </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="R554" t="inlineStr">
         <is>
           <t>BALDONI Lea</t>
@@ -34724,6 +34794,11 @@
       <c r="K555" t="n">
         <v>554</v>
       </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="R555" t="inlineStr">
         <is>
           <t>ALTMAN Marcella</t>
@@ -34787,6 +34862,11 @@
       <c r="K556" t="n">
         <v>555</v>
       </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R556" t="inlineStr">
         <is>
           <t>PANKOVA Zuzana</t>
@@ -34850,6 +34930,11 @@
       <c r="K557" t="n">
         <v>556</v>
       </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R557" t="inlineStr">
         <is>
           <t>STANOVSKA Sona</t>
@@ -34913,6 +34998,11 @@
       <c r="K558" t="n">
         <v>557</v>
       </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="R558" t="inlineStr">
         <is>
           <t>NOVAK Ajda</t>
@@ -34976,6 +35066,11 @@
       <c r="K559" t="n">
         <v>558</v>
       </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R559" t="inlineStr">
         <is>
           <t>SABATTINI Chiara</t>
@@ -35039,6 +35134,11 @@
       <c r="K560" t="n">
         <v>559</v>
       </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="R560" t="inlineStr">
         <is>
           <t>HOCEVAR Eva Alina</t>
@@ -35102,6 +35202,11 @@
       <c r="K561" t="n">
         <v>560</v>
       </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="R561" t="inlineStr">
         <is>
           <t>LAZKANO Miren</t>
@@ -35165,6 +35270,11 @@
       <c r="K562" t="n">
         <v>561</v>
       </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="R562" t="inlineStr">
         <is>
           <t>PINTERIC Naja</t>
@@ -35228,6 +35338,11 @@
       <c r="K563" t="n">
         <v>562</v>
       </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="R563" t="inlineStr">
         <is>
           <t>BOUZIDI Carole</t>
@@ -35291,6 +35406,11 @@
       <c r="K564" t="n">
         <v>563</v>
       </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="R564" t="inlineStr">
         <is>
           <t>TEUNISSEN Lena</t>
@@ -35354,6 +35474,11 @@
       <c r="K565" t="n">
         <v>564</v>
       </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="R565" t="inlineStr">
         <is>
           <t>XIE Xueting</t>
@@ -35417,6 +35542,11 @@
       <c r="K566" t="n">
         <v>565</v>
       </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="R566" t="inlineStr">
         <is>
           <t>US Viktoriia</t>
@@ -35480,6 +35610,11 @@
       <c r="K567" t="n">
         <v>566</v>
       </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R567" t="inlineStr">
         <is>
           <t>KNEBLOVA Tereza</t>
@@ -35543,6 +35678,11 @@
       <c r="K568" t="n">
         <v>567</v>
       </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="R568" t="inlineStr">
         <is>
           <t>ZWOLINSKA Klaudia</t>
@@ -35606,6 +35746,11 @@
       <c r="K569" t="n">
         <v>568</v>
       </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="R569" t="inlineStr">
         <is>
           <t>DORIA Monica</t>
@@ -35669,6 +35814,11 @@
       <c r="K570" t="n">
         <v>569</v>
       </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R570" t="inlineStr">
         <is>
           <t>FOX Jessica</t>
@@ -35732,6 +35882,11 @@
       <c r="K571" t="n">
         <v>570</v>
       </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="R571" t="inlineStr">
         <is>
           <t>SETCHELL Nikita</t>
@@ -35795,6 +35950,11 @@
       <c r="K572" t="n">
         <v>571</v>
       </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R572" t="inlineStr">
         <is>
           <t>LILIK Elena</t>
@@ -35858,6 +36018,11 @@
       <c r="K573" t="n">
         <v>572</v>
       </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R573" t="inlineStr">
         <is>
           <t>VUITTON Emma</t>
@@ -35921,6 +36086,11 @@
       <c r="K574" t="n">
         <v>573</v>
       </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R574" t="inlineStr">
         <is>
           <t>LEIBFARTH Evy</t>
@@ -35984,6 +36154,11 @@
       <c r="K575" t="n">
         <v>574</v>
       </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R575" t="inlineStr">
         <is>
           <t>FUNK Ricarda</t>
@@ -36047,6 +36222,11 @@
       <c r="K576" t="n">
         <v>575</v>
       </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="R576" t="inlineStr">
         <is>
           <t>MARX Alena</t>
@@ -36110,6 +36290,11 @@
       <c r="K577" t="n">
         <v>576</v>
       </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R577" t="inlineStr">
         <is>
           <t>CHOURRAUT Maialen</t>
@@ -36173,6 +36358,11 @@
       <c r="K578" t="n">
         <v>577</v>
       </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R578" t="inlineStr">
         <is>
           <t>FOX Noemie</t>
@@ -36236,6 +36426,11 @@
       <c r="K579" t="n">
         <v>578</v>
       </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R579" t="inlineStr">
         <is>
           <t>PRIGENT Camille</t>
@@ -36299,6 +36494,11 @@
       <c r="K580" t="n">
         <v>579</v>
       </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R580" t="inlineStr">
         <is>
           <t>HUG Angele</t>
@@ -36362,6 +36562,11 @@
       <c r="K581" t="n">
         <v>580</v>
       </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R581" t="inlineStr">
         <is>
           <t>WOODS Kimberley</t>
@@ -36425,6 +36630,11 @@
       <c r="K582" t="n">
         <v>581</v>
       </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="R582" t="inlineStr">
         <is>
           <t>EIGEL Pavel</t>
@@ -36488,6 +36698,11 @@
       <c r="K583" t="n">
         <v>582</v>
       </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
       <c r="R583" t="inlineStr">
         <is>
           <t>RAW Brayden</t>
@@ -36551,6 +36766,11 @@
       <c r="K584" t="n">
         <v>583</v>
       </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="R584" t="inlineStr">
         <is>
           <t>VAN HEERDEN Matthew</t>
@@ -36614,6 +36834,11 @@
       <c r="K585" t="n">
         <v>584</v>
       </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="R585" t="inlineStr">
         <is>
           <t>MUTO Yusuke</t>
@@ -36677,6 +36902,11 @@
       <c r="K586" t="n">
         <v>585</v>
       </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="R586" t="inlineStr">
         <is>
           <t>TEMIRGALIEV Djanibek</t>
@@ -36740,6 +36970,11 @@
       <c r="K587" t="n">
         <v>586</v>
       </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="R587" t="inlineStr">
         <is>
           <t>MING Xingzhou</t>
@@ -36803,6 +37038,11 @@
       <c r="K588" t="n">
         <v>587</v>
       </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="R588" t="inlineStr">
         <is>
           <t>MAPELLI Guilherme</t>
@@ -36866,6 +37106,11 @@
       <c r="K589" t="n">
         <v>588</v>
       </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="R589" t="inlineStr">
         <is>
           <t>ZHANG Hejie</t>
@@ -36929,6 +37174,11 @@
       <c r="K590" t="n">
         <v>589</v>
       </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="R590" t="inlineStr">
         <is>
           <t>RUDORFER Martin</t>
@@ -36992,6 +37242,11 @@
       <c r="K591" t="n">
         <v>590</v>
       </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="R591" t="inlineStr">
         <is>
           <t>GONSENICA Adam</t>
@@ -37055,6 +37310,11 @@
       <c r="K592" t="n">
         <v>591</v>
       </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="R592" t="inlineStr">
         <is>
           <t>MAGAN Raage</t>
@@ -37118,6 +37378,11 @@
       <c r="K593" t="n">
         <v>592</v>
       </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="R593" t="inlineStr">
         <is>
           <t>MAGAN Aar</t>
@@ -37181,6 +37446,11 @@
       <c r="K594" t="n">
         <v>593</v>
       </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="R594" t="inlineStr">
         <is>
           <t>TANAKA Yuuki</t>
@@ -37244,6 +37514,11 @@
       <c r="K595" t="n">
         <v>594</v>
       </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="R595" t="inlineStr">
         <is>
           <t>ZEITLHOFER Simon</t>
@@ -37370,6 +37645,11 @@
       <c r="K597" t="n">
         <v>596</v>
       </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="R597" t="inlineStr">
         <is>
           <t>GRIGAR Jakub</t>
@@ -37433,6 +37713,11 @@
       <c r="K598" t="n">
         <v>597</v>
       </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="R598" t="inlineStr">
         <is>
           <t>ROZENTALS Klass Francisks</t>
@@ -37496,6 +37781,11 @@
       <c r="K599" t="n">
         <v>598</v>
       </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="R599" t="inlineStr">
         <is>
           <t>BARAT Andy</t>
@@ -37622,6 +37912,11 @@
       <c r="K601" t="n">
         <v>600</v>
       </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="R601" t="inlineStr">
         <is>
           <t>UKALOVIC Thomas</t>
@@ -37685,6 +37980,11 @@
       <c r="K602" t="n">
         <v>601</v>
       </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R602" t="inlineStr">
         <is>
           <t>HUANG Liman</t>
@@ -37748,6 +38048,11 @@
       <c r="K603" t="n">
         <v>602</v>
       </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="R603" t="inlineStr">
         <is>
           <t>ZIELONKA Mark</t>
@@ -37811,6 +38116,11 @@
       <c r="K604" t="n">
         <v>603</v>
       </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="R604" t="inlineStr">
         <is>
           <t>BOYD Trevor</t>
@@ -37874,6 +38184,11 @@
       <c r="K605" t="n">
         <v>604</v>
       </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="R605" t="inlineStr">
         <is>
           <t>PUCHNER Oliver</t>
@@ -37937,6 +38252,11 @@
       <c r="K606" t="n">
         <v>605</v>
       </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="R606" t="inlineStr">
         <is>
           <t>TRIPANO Manuel</t>
@@ -38000,6 +38320,11 @@
       <c r="K607" t="n">
         <v>606</v>
       </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="R607" t="inlineStr">
         <is>
           <t>BRZEZINSKI Jakub</t>
@@ -38063,6 +38388,11 @@
       <c r="K608" t="n">
         <v>607</v>
       </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="R608" t="inlineStr">
         <is>
           <t>ECHANIZ Pau</t>
@@ -38126,6 +38456,11 @@
       <c r="K609" t="n">
         <v>608</v>
       </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="R609" t="inlineStr">
         <is>
           <t>FERRAZZI Xabier</t>
@@ -38189,6 +38524,11 @@
       <c r="K610" t="n">
         <v>609</v>
       </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R610" t="inlineStr">
         <is>
           <t>AUBERTIN Maxime</t>
@@ -38252,6 +38592,11 @@
       <c r="K611" t="n">
         <v>610</v>
       </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="R611" t="inlineStr">
         <is>
           <t>NOVAK Matyas</t>
@@ -38315,6 +38660,11 @@
       <c r="K612" t="n">
         <v>611</v>
       </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="R612" t="inlineStr">
         <is>
           <t>PASIUT Michal</t>
@@ -38378,6 +38728,11 @@
       <c r="K613" t="n">
         <v>612</v>
       </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="R613" t="inlineStr">
         <is>
           <t>MARTINEZ Jesus</t>
@@ -38441,6 +38796,11 @@
       <c r="K614" t="n">
         <v>613</v>
       </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="R614" t="inlineStr">
         <is>
           <t>KUDER MARUSIC Vid</t>
@@ -38504,6 +38864,11 @@
       <c r="K615" t="n">
         <v>614</v>
       </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="R615" t="inlineStr">
         <is>
           <t>MCCREERY Alistair</t>
@@ -38630,6 +38995,11 @@
       <c r="K617" t="n">
         <v>616</v>
       </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="R617" t="inlineStr">
         <is>
           <t>COLLIER Nicholas</t>
@@ -38693,6 +39063,11 @@
       <c r="K618" t="n">
         <v>617</v>
       </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="R618" t="inlineStr">
         <is>
           <t>POPE Benjamin</t>
@@ -38756,6 +39131,11 @@
       <c r="K619" t="n">
         <v>618</v>
       </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="R619" t="inlineStr">
         <is>
           <t>ROELLER Tillmann</t>
@@ -38819,6 +39199,11 @@
       <c r="K620" t="n">
         <v>619</v>
       </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="R620" t="inlineStr">
         <is>
           <t>KANCLER Tine</t>
@@ -38882,6 +39267,11 @@
       <c r="K621" t="n">
         <v>620</v>
       </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="R621" t="inlineStr">
         <is>
           <t>OHRSTROM Isak</t>
@@ -38945,6 +39335,11 @@
       <c r="K622" t="n">
         <v>621</v>
       </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="R622" t="inlineStr">
         <is>
           <t>LONG Kyler James</t>
@@ -39071,6 +39466,11 @@
       <c r="K624" t="n">
         <v>623</v>
       </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="R624" t="inlineStr">
         <is>
           <t>BALDONI Alex</t>
@@ -39134,6 +39534,11 @@
       <c r="K625" t="n">
         <v>624</v>
       </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R625" t="inlineStr">
         <is>
           <t>DE COSTER Gabriel</t>
@@ -39197,6 +39602,11 @@
       <c r="K626" t="n">
         <v>625</v>
       </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="R626" t="inlineStr">
         <is>
           <t>CHIARELLO Gelindo</t>
@@ -39260,6 +39670,11 @@
       <c r="K627" t="n">
         <v>626</v>
       </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R627" t="inlineStr">
         <is>
           <t>HENGST Stefan</t>
@@ -39323,6 +39738,11 @@
       <c r="K628" t="n">
         <v>627</v>
       </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R628" t="inlineStr">
         <is>
           <t>KREJCI Jakub</t>
@@ -39386,6 +39806,11 @@
       <c r="K629" t="n">
         <v>628</v>
       </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R629" t="inlineStr">
         <is>
           <t>HOCEVAR Ziga Lin</t>
@@ -39449,6 +39874,11 @@
       <c r="K630" t="n">
         <v>629</v>
       </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="R630" t="inlineStr">
         <is>
           <t>HOLMER Erik</t>
@@ -39512,6 +39942,11 @@
       <c r="K631" t="n">
         <v>630</v>
       </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="R631" t="inlineStr">
         <is>
           <t>DELFOUR Lucien</t>
@@ -39575,6 +40010,11 @@
       <c r="K632" t="n">
         <v>631</v>
       </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R632" t="inlineStr">
         <is>
           <t>OSCHMAUTZ Felix</t>
@@ -39638,6 +40078,11 @@
       <c r="K633" t="n">
         <v>632</v>
       </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R633" t="inlineStr">
         <is>
           <t>CASTRYCK Titouan</t>
@@ -39701,6 +40146,11 @@
       <c r="K634" t="n">
         <v>633</v>
       </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="R634" t="inlineStr">
         <is>
           <t>LEAVER Sam</t>
@@ -39764,6 +40214,11 @@
       <c r="K635" t="n">
         <v>634</v>
       </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="R635" t="inlineStr">
         <is>
           <t>ANDERSON Timothy</t>
@@ -39827,6 +40282,11 @@
       <c r="K636" t="n">
         <v>635</v>
       </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="R636" t="inlineStr">
         <is>
           <t>DICKSON Jonny</t>
@@ -39890,6 +40350,11 @@
       <c r="K637" t="n">
         <v>636</v>
       </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="R637" t="inlineStr">
         <is>
           <t>ECHEVERRIA OLGUIN Andraz</t>
@@ -39953,6 +40418,11 @@
       <c r="K638" t="n">
         <v>637</v>
       </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R638" t="inlineStr">
         <is>
           <t>ROHRER Jan</t>
@@ -40016,6 +40486,11 @@
       <c r="K639" t="n">
         <v>638</v>
       </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R639" t="inlineStr">
         <is>
           <t>MADORE Mathurin</t>
@@ -40079,6 +40554,11 @@
       <c r="K640" t="n">
         <v>639</v>
       </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="R640" t="inlineStr">
         <is>
           <t>GONCALVES Pedro</t>
@@ -40142,6 +40622,11 @@
       <c r="K641" t="n">
         <v>640</v>
       </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R641" t="inlineStr">
         <is>
           <t>OCHOA Manuel</t>
@@ -40205,6 +40690,11 @@
       <c r="K642" t="n">
         <v>641</v>
       </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R642" t="inlineStr">
         <is>
           <t>HEGGE Noah</t>
@@ -40268,6 +40758,11 @@
       <c r="K643" t="n">
         <v>642</v>
       </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R643" t="inlineStr">
         <is>
           <t>DE GENNARO Giovanni</t>
@@ -40331,6 +40826,11 @@
       <c r="K644" t="n">
         <v>643</v>
       </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R644" t="inlineStr">
         <is>
           <t>POLACZYK Mateusz</t>
@@ -40394,6 +40894,11 @@
       <c r="K645" t="n">
         <v>644</v>
       </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="R645" t="inlineStr">
         <is>
           <t>LLORENTE David</t>
@@ -40457,6 +40962,11 @@
       <c r="K646" t="n">
         <v>645</v>
       </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R646" t="inlineStr">
         <is>
           <t>RENIA Benjamin</t>
@@ -40520,6 +41030,11 @@
       <c r="K647" t="n">
         <v>646</v>
       </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="R647" t="inlineStr">
         <is>
           <t>DOUGOUD Martin</t>
@@ -40583,6 +41098,11 @@
       <c r="K648" t="n">
         <v>647</v>
       </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R648" t="inlineStr">
         <is>
           <t>BUTCHER Finn</t>
@@ -40645,6 +41165,11 @@
       </c>
       <c r="K649" t="n">
         <v>648</v>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="R649" t="inlineStr">
         <is>
